--- a/TFD 3-1/Regular Assessment TFD 3-1.xlsx
+++ b/TFD 3-1/Regular Assessment TFD 3-1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Attendance\TFD 3-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99FBA9C-DEBE-4DBB-A43B-E8F7D65C7D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3143D0E-D3C9-41F4-A2FC-28BFECAAB0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="49">
   <si>
     <t>SL</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>P</t>
   </si>
 </sst>
 </file>
@@ -677,7 +683,7 @@
     <col min="2" max="2" width="18.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
@@ -817,7 +823,7 @@
         <v>39</v>
       </c>
       <c r="E3" s="5">
-        <v>46249</v>
+        <v>46267</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -849,11 +855,13 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="10" t="e">
+      <c r="D4" s="10">
         <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E4" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
@@ -885,11 +893,13 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="10" t="e">
+      <c r="D5" s="10">
         <f t="shared" ref="D5:D33" si="1">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E5" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
@@ -921,11 +931,13 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E6" s="1"/>
+      <c r="D6" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -957,11 +969,13 @@
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E7" s="1"/>
+      <c r="D7" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -993,11 +1007,13 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E8" s="1"/>
+      <c r="D8" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
@@ -1029,11 +1045,13 @@
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E9" s="1"/>
+      <c r="D9" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
@@ -1065,11 +1083,13 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E10" s="1"/>
+      <c r="D10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
@@ -1101,11 +1121,13 @@
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E11" s="1"/>
+      <c r="D11" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
@@ -1137,11 +1159,13 @@
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E12" s="1"/>
+      <c r="D12" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
@@ -1173,11 +1197,13 @@
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E13" s="1"/>
+      <c r="D13" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
@@ -1209,11 +1235,13 @@
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E14" s="1"/>
+      <c r="D14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
@@ -1245,11 +1273,13 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E15" s="1"/>
+      <c r="D15" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
@@ -1281,11 +1311,13 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E16" s="1"/>
+      <c r="D16" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
@@ -1317,11 +1349,13 @@
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E17" s="1"/>
+      <c r="D17" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
@@ -1353,11 +1387,13 @@
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E18" s="1"/>
+      <c r="D18" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
@@ -1389,11 +1425,13 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E19" s="1"/>
+      <c r="D19" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
@@ -1425,11 +1463,13 @@
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E20" s="1"/>
+      <c r="D20" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
@@ -1461,11 +1501,13 @@
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E21" s="1"/>
+      <c r="D21" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
@@ -1497,11 +1539,13 @@
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E22" s="1"/>
+      <c r="D22" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -1533,11 +1577,13 @@
       <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E23" s="1"/>
+      <c r="D23" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
@@ -1569,11 +1615,13 @@
       <c r="C24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E24" s="1"/>
+      <c r="D24" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
@@ -1605,11 +1653,13 @@
       <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E25" s="1"/>
+      <c r="D25" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
@@ -1641,11 +1691,13 @@
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E26" s="1"/>
+      <c r="D26" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
@@ -1677,11 +1729,13 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E27" s="1"/>
+      <c r="D27" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
@@ -1713,11 +1767,13 @@
       <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E28" s="1"/>
+      <c r="D28" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
       <c r="H28" s="12"/>
@@ -1749,11 +1805,13 @@
       <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E29" s="1"/>
+      <c r="D29" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
@@ -1785,11 +1843,13 @@
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E30" s="1"/>
+      <c r="D30" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
@@ -1821,11 +1881,13 @@
       <c r="C31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E31" s="1"/>
+      <c r="D31" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
@@ -1857,11 +1919,13 @@
       <c r="C32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E32" s="1"/>
+      <c r="D32" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
@@ -1893,11 +1957,13 @@
       <c r="C33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E33" s="1"/>
+      <c r="D33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>

--- a/TFD 3-1/Regular Assessment TFD 3-1.xlsx
+++ b/TFD 3-1/Regular Assessment TFD 3-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3143D0E-D3C9-41F4-A2FC-28BFECAAB0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5739A094-3217-4915-BD66-7A1D8801BA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TFD 3-1 Attendance'!$A$3:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TFD 3-1 Attendance'!$A$3:$E$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -195,7 +195,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,8 +236,21 @@
       <name val="Gill Sans MT"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,6 +305,11 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -317,10 +335,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -353,7 +372,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -375,8 +393,14 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -677,21 +701,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="8.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="3"/>
+    <col min="5" max="5" width="40.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="A1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="17"/>
       <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
@@ -717,7 +741,7 @@
       <c r="W1" s="8"/>
       <c r="X1" s="8"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -845,7 +869,7 @@
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -862,27 +886,27 @@
       <c r="E4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A5" s="1">
         <f>A4+1</f>
         <v>2</v>
@@ -900,27 +924,27 @@
       <c r="E5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="21"/>
+      <c r="X5" s="21"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A33" si="2">A5+1</f>
         <v>3</v>
@@ -938,27 +962,27 @@
       <c r="E6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="21"/>
+      <c r="X6" s="21"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -976,27 +1000,27 @@
       <c r="E7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="21"/>
+      <c r="W7" s="21"/>
+      <c r="X7" s="21"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -1014,27 +1038,27 @@
       <c r="E8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="21"/>
+      <c r="X8" s="21"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -1052,27 +1076,27 @@
       <c r="E9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="12"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
+      <c r="X9" s="21"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A10" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -1087,30 +1111,30 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="21"/>
+      <c r="X10" s="21"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A11" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -1128,27 +1152,27 @@
       <c r="E11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="21"/>
+      <c r="W11" s="21"/>
+      <c r="X11" s="21"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -1166,28 +1190,28 @@
       <c r="E12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="A13" s="12">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
@@ -1204,27 +1228,27 @@
       <c r="E13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -1239,30 +1263,30 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -1280,27 +1304,27 @@
       <c r="E15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="12"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="21"/>
+      <c r="X15" s="21"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -1318,27 +1342,27 @@
       <c r="E16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="12"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="21"/>
+      <c r="X16" s="21"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -1356,27 +1380,27 @@
       <c r="E17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
+      <c r="V17" s="21"/>
+      <c r="W17" s="21"/>
+      <c r="X17" s="21"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1391,30 +1415,30 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="21"/>
+      <c r="X18" s="21"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -1432,27 +1456,27 @@
       <c r="E19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -1470,27 +1494,27 @@
       <c r="E20" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="12"/>
-      <c r="S20" s="12"/>
-      <c r="T20" s="12"/>
-      <c r="U20" s="12"/>
-      <c r="V20" s="12"/>
-      <c r="W20" s="12"/>
-      <c r="X20" s="12"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+      <c r="V20" s="21"/>
+      <c r="W20" s="21"/>
+      <c r="X20" s="21"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -1508,27 +1532,27 @@
       <c r="E21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="21"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="21"/>
+      <c r="U21" s="21"/>
+      <c r="V21" s="21"/>
+      <c r="W21" s="21"/>
+      <c r="X21" s="21"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -1546,27 +1570,27 @@
       <c r="E22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="21"/>
+      <c r="U22" s="21"/>
+      <c r="V22" s="21"/>
+      <c r="W22" s="21"/>
+      <c r="X22" s="21"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -1584,27 +1608,27 @@
       <c r="E23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="21"/>
+      <c r="S23" s="21"/>
+      <c r="T23" s="21"/>
+      <c r="U23" s="21"/>
+      <c r="V23" s="21"/>
+      <c r="W23" s="21"/>
+      <c r="X23" s="21"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -1622,27 +1646,27 @@
       <c r="E24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="12"/>
-      <c r="V24" s="12"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="21"/>
+      <c r="U24" s="21"/>
+      <c r="V24" s="21"/>
+      <c r="W24" s="21"/>
+      <c r="X24" s="21"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -1660,27 +1684,27 @@
       <c r="E25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="12"/>
-      <c r="U25" s="12"/>
-      <c r="V25" s="12"/>
-      <c r="W25" s="12"/>
-      <c r="X25" s="12"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="21"/>
+      <c r="S25" s="21"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="21"/>
+      <c r="V25" s="21"/>
+      <c r="W25" s="21"/>
+      <c r="X25" s="21"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -1698,27 +1722,27 @@
       <c r="E26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="12"/>
-      <c r="U26" s="12"/>
-      <c r="V26" s="12"/>
-      <c r="W26" s="12"/>
-      <c r="X26" s="12"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="21"/>
+      <c r="W26" s="21"/>
+      <c r="X26" s="21"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -1736,27 +1760,27 @@
       <c r="E27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="21"/>
+      <c r="U27" s="21"/>
+      <c r="V27" s="21"/>
+      <c r="W27" s="21"/>
+      <c r="X27" s="21"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -1774,27 +1798,27 @@
       <c r="E28" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
-      <c r="U28" s="12"/>
-      <c r="V28" s="12"/>
-      <c r="W28" s="12"/>
-      <c r="X28" s="12"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="21"/>
+      <c r="S28" s="21"/>
+      <c r="T28" s="21"/>
+      <c r="U28" s="21"/>
+      <c r="V28" s="21"/>
+      <c r="W28" s="21"/>
+      <c r="X28" s="21"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -1812,27 +1836,27 @@
       <c r="E29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="12"/>
-      <c r="X29" s="12"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="21"/>
+      <c r="R29" s="21"/>
+      <c r="S29" s="21"/>
+      <c r="T29" s="21"/>
+      <c r="U29" s="21"/>
+      <c r="V29" s="21"/>
+      <c r="W29" s="21"/>
+      <c r="X29" s="21"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -1847,30 +1871,30 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="12"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
+      <c r="O30" s="21"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="21"/>
+      <c r="R30" s="21"/>
+      <c r="S30" s="21"/>
+      <c r="T30" s="21"/>
+      <c r="U30" s="21"/>
+      <c r="V30" s="21"/>
+      <c r="W30" s="21"/>
+      <c r="X30" s="21"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -1888,27 +1912,27 @@
       <c r="E31" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="12"/>
-      <c r="W31" s="12"/>
-      <c r="X31" s="12"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="21"/>
+      <c r="T31" s="21"/>
+      <c r="U31" s="21"/>
+      <c r="V31" s="21"/>
+      <c r="W31" s="21"/>
+      <c r="X31" s="21"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A32" s="1">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -1926,27 +1950,27 @@
       <c r="E32" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="12"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="12"/>
-      <c r="T32" s="12"/>
-      <c r="U32" s="12"/>
-      <c r="V32" s="12"/>
-      <c r="W32" s="12"/>
-      <c r="X32" s="12"/>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
+      <c r="R32" s="21"/>
+      <c r="S32" s="21"/>
+      <c r="T32" s="21"/>
+      <c r="U32" s="21"/>
+      <c r="V32" s="21"/>
+      <c r="W32" s="21"/>
+      <c r="X32" s="21"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A33" s="1">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -1961,31 +1985,31 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="12"/>
-      <c r="U33" s="12"/>
-      <c r="V33" s="12"/>
-      <c r="W33" s="12"/>
-      <c r="X33" s="12"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="21"/>
+      <c r="S33" s="21"/>
+      <c r="T33" s="21"/>
+      <c r="U33" s="21"/>
+      <c r="V33" s="21"/>
+      <c r="W33" s="21"/>
+      <c r="X33" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:E33" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -2017,29 +2041,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="17"/>
       <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="19"/>
+      <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -2052,14 +2076,14 @@
       <c r="C2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
     </row>
     <row r="3" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -2071,22 +2095,22 @@
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="15">
         <v>20</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="15">
         <v>7.5</v>
       </c>
     </row>
@@ -2100,15 +2124,15 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16">
         <f>SUM(D4:G4)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="16">
         <f>(H4/20)*7.5</f>
         <v>0</v>
       </c>
@@ -2124,15 +2148,15 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16">
         <f t="shared" ref="H5:H33" si="0">SUM(D5:G5)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="16">
         <f t="shared" ref="I5:I33" si="1">(H5/20)*7.5</f>
         <v>0</v>
       </c>
@@ -2148,15 +2172,15 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="17">
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2172,15 +2196,15 @@
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="17">
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2196,15 +2220,15 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="17">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2220,15 +2244,15 @@
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="17">
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2244,15 +2268,15 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="17">
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2268,15 +2292,15 @@
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="17">
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2292,21 +2316,21 @@
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="17">
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
+      <c r="A13" s="12">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
@@ -2316,15 +2340,15 @@
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="17">
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2340,15 +2364,15 @@
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="17">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2364,15 +2388,15 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="17">
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2388,15 +2412,15 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="17">
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2412,15 +2436,15 @@
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="17">
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2436,15 +2460,15 @@
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="17">
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2460,15 +2484,15 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="17">
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2484,15 +2508,15 @@
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="17">
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2508,15 +2532,15 @@
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="17">
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2532,15 +2556,15 @@
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="17">
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2556,15 +2580,15 @@
       <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="17">
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2580,15 +2604,15 @@
       <c r="C24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="17">
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2604,15 +2628,15 @@
       <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="17">
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2628,15 +2652,15 @@
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="17">
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2652,15 +2676,15 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="17">
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2676,15 +2700,15 @@
       <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="17">
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2700,15 +2724,15 @@
       <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="17">
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2724,15 +2748,15 @@
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="17">
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2748,15 +2772,15 @@
       <c r="C31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="17">
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2776,11 +2800,11 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="17">
+      <c r="H32" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2800,11 +2824,11 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="17">
+      <c r="H33" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>

--- a/TFD 3-1/Regular Assessment TFD 3-1.xlsx
+++ b/TFD 3-1/Regular Assessment TFD 3-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5739A094-3217-4915-BD66-7A1D8801BA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E003F2D9-1787-4683-87FD-6B7E9E536BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TFD 3-1 Attendance'!$A$3:$E$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TFD 3-1 Attendance'!$A$3:$E$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="50">
   <si>
     <t>SL</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>P</t>
+  </si>
+  <si>
+    <t>TFD 3-1</t>
   </si>
 </sst>
 </file>
@@ -339,7 +342,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -387,17 +390,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -700,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="11" bestFit="1" customWidth="1"/>
@@ -708,14 +718,15 @@
     <col min="3" max="3" width="34.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="20"/>
+    <col min="6" max="6" width="30.77734375" style="18" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.5">
-      <c r="A1" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="17"/>
+      <c r="A1" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="21"/>
       <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
@@ -746,8 +757,8 @@
         <v>35</v>
       </c>
       <c r="B2" s="7">
-        <f>COUNT(A4:A33)</f>
-        <v>30</v>
+        <f>COUNT(A4:A31)</f>
+        <v>28</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>36</v>
@@ -833,7 +844,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -849,7 +860,9 @@
       <c r="E3" s="5">
         <v>46267</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="F3" s="5">
+        <v>46271</v>
+      </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -886,25 +899,27 @@
       <c r="E4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="21"/>
-      <c r="X4" s="21"/>
+      <c r="F4" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A5" s="1">
@@ -918,35 +933,37 @@
         <v>4</v>
       </c>
       <c r="D5" s="10">
-        <f t="shared" ref="D5:D33" si="1">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
+        <f t="shared" ref="D5:D31" si="1">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="21"/>
-      <c r="X5" s="21"/>
+      <c r="F5" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A33" si="2">A5+1</f>
+        <f t="shared" ref="A6:A31" si="2">A5+1</f>
         <v>3</v>
       </c>
       <c r="B6" s="1">
@@ -962,25 +979,27 @@
       <c r="E6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="21"/>
-      <c r="V6" s="21"/>
-      <c r="W6" s="21"/>
-      <c r="X6" s="21"/>
+      <c r="F6" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A7" s="1">
@@ -1000,25 +1019,27 @@
       <c r="E7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="21"/>
-      <c r="V7" s="21"/>
-      <c r="W7" s="21"/>
-      <c r="X7" s="21"/>
+      <c r="F7" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A8" s="1">
@@ -1038,25 +1059,27 @@
       <c r="E8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="21"/>
-      <c r="V8" s="21"/>
-      <c r="W8" s="21"/>
-      <c r="X8" s="21"/>
+      <c r="F8" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A9" s="1">
@@ -1076,25 +1099,27 @@
       <c r="E9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="21"/>
-      <c r="V9" s="21"/>
-      <c r="W9" s="21"/>
-      <c r="X9" s="21"/>
+      <c r="F9" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A10" s="1">
@@ -1102,37 +1127,39 @@
         <v>7</v>
       </c>
       <c r="B10" s="1">
-        <v>24010601010</v>
+        <v>24010601011</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E10" s="19" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="21"/>
-      <c r="R10" s="21"/>
-      <c r="S10" s="21"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="21"/>
-      <c r="V10" s="21"/>
-      <c r="W10" s="21"/>
-      <c r="X10" s="21"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A11" s="1">
@@ -1140,10 +1167,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="1">
-        <v>24010601011</v>
+        <v>24010601014</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="10">
         <f t="shared" si="1"/>
@@ -1152,25 +1179,27 @@
       <c r="E11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
+      <c r="F11" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A12" s="1">
@@ -1178,10 +1207,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="1">
-        <v>24010601014</v>
+        <v>24010601015</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="1"/>
@@ -1190,63 +1219,67 @@
       <c r="E12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="21"/>
-      <c r="V12" s="21"/>
-      <c r="W12" s="21"/>
-      <c r="X12" s="21"/>
+      <c r="F12" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.5">
-      <c r="A13" s="12">
+      <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="B13" s="1">
-        <v>24010601015</v>
+        <v>24010601017</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
+      <c r="F13" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A14" s="1">
@@ -1254,37 +1287,39 @@
         <v>11</v>
       </c>
       <c r="B14" s="1">
-        <v>24010601016</v>
+        <v>24010601018</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="21"/>
-      <c r="X14" s="21"/>
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A15" s="1">
@@ -1292,10 +1327,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="1">
-        <v>24010601017</v>
+        <v>24010601019</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="1"/>
@@ -1304,25 +1339,27 @@
       <c r="E15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="21"/>
+      <c r="F15" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A16" s="1">
@@ -1330,37 +1367,39 @@
         <v>13</v>
       </c>
       <c r="B16" s="1">
-        <v>24010601018</v>
+        <v>24010601022</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
-      <c r="V16" s="21"/>
-      <c r="W16" s="21"/>
-      <c r="X16" s="21"/>
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A17" s="1">
@@ -1368,37 +1407,39 @@
         <v>14</v>
       </c>
       <c r="B17" s="1">
-        <v>24010601019</v>
+        <v>24010601023</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
-      <c r="V17" s="21"/>
-      <c r="W17" s="21"/>
-      <c r="X17" s="21"/>
+      <c r="F17" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A18" s="1">
@@ -1406,37 +1447,39 @@
         <v>15</v>
       </c>
       <c r="B18" s="1">
-        <v>24010601022</v>
+        <v>24010601024</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E18" s="19" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="21"/>
-      <c r="W18" s="21"/>
-      <c r="X18" s="21"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A19" s="1">
@@ -1444,10 +1487,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="1">
-        <v>24010601023</v>
+        <v>24010601025</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="1"/>
@@ -1456,25 +1499,27 @@
       <c r="E19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="21"/>
-      <c r="X19" s="21"/>
+      <c r="F19" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A20" s="1">
@@ -1482,10 +1527,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="1">
-        <v>24010601024</v>
+        <v>24010601026</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="1"/>
@@ -1494,25 +1539,27 @@
       <c r="E20" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="21"/>
-      <c r="W20" s="21"/>
-      <c r="X20" s="21"/>
+      <c r="F20" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A21" s="1">
@@ -1520,10 +1567,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="1">
-        <v>24010601025</v>
+        <v>24010601027</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="1"/>
@@ -1532,25 +1579,27 @@
       <c r="E21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="21"/>
-      <c r="W21" s="21"/>
-      <c r="X21" s="21"/>
+      <c r="F21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A22" s="1">
@@ -1558,37 +1607,39 @@
         <v>19</v>
       </c>
       <c r="B22" s="1">
-        <v>24010601026</v>
+        <v>24010601028</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="21"/>
-      <c r="W22" s="21"/>
-      <c r="X22" s="21"/>
+      <c r="F22" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A23" s="1">
@@ -1596,10 +1647,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="1">
-        <v>24010601027</v>
+        <v>24010601029</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="1"/>
@@ -1608,25 +1659,27 @@
       <c r="E23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
-      <c r="V23" s="21"/>
-      <c r="W23" s="21"/>
-      <c r="X23" s="21"/>
+      <c r="F23" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A24" s="1">
@@ -1634,10 +1687,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="1">
-        <v>24010601028</v>
+        <v>24010601031</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="1"/>
@@ -1646,25 +1699,27 @@
       <c r="E24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-      <c r="V24" s="21"/>
-      <c r="W24" s="21"/>
-      <c r="X24" s="21"/>
+      <c r="F24" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A25" s="1">
@@ -1672,10 +1727,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="1">
-        <v>24010601029</v>
+        <v>24010601032</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="1"/>
@@ -1684,25 +1739,27 @@
       <c r="E25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-      <c r="V25" s="21"/>
-      <c r="W25" s="21"/>
-      <c r="X25" s="21"/>
+      <c r="F25" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="20"/>
+      <c r="X25" s="20"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A26" s="1">
@@ -1710,10 +1767,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="1">
-        <v>24010601031</v>
+        <v>24010601033</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="1"/>
@@ -1722,25 +1779,27 @@
       <c r="E26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-      <c r="V26" s="21"/>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
+      <c r="F26" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A27" s="1">
@@ -1748,10 +1807,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="1">
-        <v>24010601032</v>
+        <v>23010601014</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="1"/>
@@ -1760,25 +1819,27 @@
       <c r="E27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
-      <c r="T27" s="21"/>
-      <c r="U27" s="21"/>
-      <c r="V27" s="21"/>
-      <c r="W27" s="21"/>
-      <c r="X27" s="21"/>
+      <c r="F27" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A28" s="1">
@@ -1786,37 +1847,39 @@
         <v>25</v>
       </c>
       <c r="B28" s="1">
-        <v>24010601033</v>
+        <v>23010601015</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="21"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
-      <c r="V28" s="21"/>
-      <c r="W28" s="21"/>
-      <c r="X28" s="21"/>
+        <v>0.5</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A29" s="1">
@@ -1824,10 +1887,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="1">
-        <v>23010601014</v>
+        <v>23010601024</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="1"/>
@@ -1836,184 +1899,114 @@
       <c r="E29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="21"/>
-      <c r="S29" s="21"/>
-      <c r="T29" s="21"/>
-      <c r="U29" s="21"/>
-      <c r="V29" s="21"/>
-      <c r="W29" s="21"/>
-      <c r="X29" s="21"/>
+      <c r="F29" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B30" s="1">
-        <v>23010601015</v>
+      <c r="B30" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="19" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="21"/>
-      <c r="S30" s="21"/>
-      <c r="T30" s="21"/>
-      <c r="U30" s="21"/>
-      <c r="V30" s="21"/>
-      <c r="W30" s="21"/>
-      <c r="X30" s="21"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.5">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="B31" s="1">
-        <v>23010601024</v>
+      <c r="B31" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="21"/>
-      <c r="P31" s="21"/>
-      <c r="Q31" s="21"/>
-      <c r="R31" s="21"/>
-      <c r="S31" s="21"/>
-      <c r="T31" s="21"/>
-      <c r="U31" s="21"/>
-      <c r="V31" s="21"/>
-      <c r="W31" s="21"/>
-      <c r="X31" s="21"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.5">
-      <c r="A32" s="1">
-        <f t="shared" si="2"/>
-        <v>29</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="10">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21"/>
-      <c r="O32" s="21"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="21"/>
-      <c r="R32" s="21"/>
-      <c r="S32" s="21"/>
-      <c r="T32" s="21"/>
-      <c r="U32" s="21"/>
-      <c r="V32" s="21"/>
-      <c r="W32" s="21"/>
-      <c r="X32" s="21"/>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.5">
-      <c r="A33" s="1">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E33" s="19" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="21"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="21"/>
-      <c r="R33" s="21"/>
-      <c r="S33" s="21"/>
-      <c r="T33" s="21"/>
-      <c r="U33" s="21"/>
-      <c r="V33" s="21"/>
-      <c r="W33" s="21"/>
-      <c r="X33" s="21"/>
+      <c r="F31" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E33" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:E31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D33">
+  <conditionalFormatting sqref="D4:D31">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
@@ -2041,10 +2034,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="21"/>
       <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
@@ -2060,10 +2053,10 @@
       <c r="G1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="18"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -2082,8 +2075,8 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/TFD 3-1/Regular Assessment TFD 3-1.xlsx
+++ b/TFD 3-1/Regular Assessment TFD 3-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E003F2D9-1787-4683-87FD-6B7E9E536BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88814CBA-D097-4328-9BD2-A5FAECA8A42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -719,7 +719,8 @@
     <col min="4" max="4" width="20.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.77734375" style="18" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="18"/>
+    <col min="7" max="7" width="35.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.5">
@@ -863,7 +864,9 @@
       <c r="F3" s="5">
         <v>46271</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="5">
+        <v>46274</v>
+      </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>

--- a/TFD 3-1/Regular Assessment TFD 3-1.xlsx
+++ b/TFD 3-1/Regular Assessment TFD 3-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88814CBA-D097-4328-9BD2-A5FAECA8A42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4D97D4-27F7-4FCD-AE88-12A70D6F83D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="50">
   <si>
     <t>SL</t>
   </si>
@@ -905,7 +905,9 @@
       <c r="F4" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="20"/>
+      <c r="G4" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
       <c r="J4" s="20"/>
@@ -945,7 +947,9 @@
       <c r="F5" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="20"/>
+      <c r="G5" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
       <c r="J5" s="20"/>
@@ -985,7 +989,9 @@
       <c r="F6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="20"/>
+      <c r="G6" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H6" s="20"/>
       <c r="I6" s="20"/>
       <c r="J6" s="20"/>
@@ -1025,7 +1031,9 @@
       <c r="F7" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="20"/>
+      <c r="G7" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
@@ -1065,7 +1073,9 @@
       <c r="F8" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="20"/>
+      <c r="G8" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H8" s="20"/>
       <c r="I8" s="20"/>
       <c r="J8" s="20"/>
@@ -1105,7 +1115,9 @@
       <c r="F9" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
       <c r="J9" s="20"/>
@@ -1137,7 +1149,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>48</v>
@@ -1145,7 +1157,9 @@
       <c r="F10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
       <c r="J10" s="20"/>
@@ -1185,7 +1199,9 @@
       <c r="F11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="20"/>
+      <c r="G11" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
@@ -1225,7 +1241,9 @@
       <c r="F12" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
       <c r="J12" s="20"/>
@@ -1257,7 +1275,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>48</v>
@@ -1265,7 +1283,9 @@
       <c r="F13" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="20"/>
+      <c r="G13" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
       <c r="J13" s="20"/>
@@ -1305,7 +1325,9 @@
       <c r="F14" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G14" s="20"/>
+      <c r="G14" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H14" s="20"/>
       <c r="I14" s="20"/>
       <c r="J14" s="20"/>
@@ -1337,7 +1359,7 @@
       </c>
       <c r="D15" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>48</v>
@@ -1345,7 +1367,9 @@
       <c r="F15" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
@@ -1377,7 +1401,7 @@
       </c>
       <c r="D16" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>47</v>
@@ -1385,7 +1409,9 @@
       <c r="F16" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H16" s="20"/>
       <c r="I16" s="20"/>
       <c r="J16" s="20"/>
@@ -1417,7 +1443,7 @@
       </c>
       <c r="D17" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>48</v>
@@ -1425,7 +1451,9 @@
       <c r="F17" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="20"/>
+      <c r="G17" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
@@ -1457,7 +1485,7 @@
       </c>
       <c r="D18" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>48</v>
@@ -1465,7 +1493,9 @@
       <c r="F18" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="20"/>
+      <c r="G18" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
       <c r="J18" s="20"/>
@@ -1505,7 +1535,9 @@
       <c r="F19" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="20"/>
+      <c r="G19" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
       <c r="J19" s="20"/>
@@ -1545,7 +1577,9 @@
       <c r="F20" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="20"/>
+      <c r="G20" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H20" s="20"/>
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
@@ -1585,7 +1619,9 @@
       <c r="F21" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G21" s="20"/>
+      <c r="G21" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
@@ -1617,7 +1653,7 @@
       </c>
       <c r="D22" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>48</v>
@@ -1625,7 +1661,9 @@
       <c r="F22" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="20"/>
+      <c r="G22" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
       <c r="J22" s="20"/>
@@ -1665,7 +1703,9 @@
       <c r="F23" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G23" s="20"/>
+      <c r="G23" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
       <c r="J23" s="20"/>
@@ -1705,7 +1745,9 @@
       <c r="F24" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G24" s="20"/>
+      <c r="G24" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H24" s="20"/>
       <c r="I24" s="20"/>
       <c r="J24" s="20"/>
@@ -1745,7 +1787,9 @@
       <c r="F25" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G25" s="20"/>
+      <c r="G25" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H25" s="20"/>
       <c r="I25" s="20"/>
       <c r="J25" s="20"/>
@@ -1785,7 +1829,9 @@
       <c r="F26" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G26" s="20"/>
+      <c r="G26" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H26" s="20"/>
       <c r="I26" s="20"/>
       <c r="J26" s="20"/>
@@ -1825,7 +1871,9 @@
       <c r="F27" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G27" s="20"/>
+      <c r="G27" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H27" s="20"/>
       <c r="I27" s="20"/>
       <c r="J27" s="20"/>
@@ -1857,7 +1905,7 @@
       </c>
       <c r="D28" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>47</v>
@@ -1865,7 +1913,9 @@
       <c r="F28" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G28" s="20"/>
+      <c r="G28" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
       <c r="J28" s="20"/>
@@ -1905,7 +1955,9 @@
       <c r="F29" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G29" s="20"/>
+      <c r="G29" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H29" s="20"/>
       <c r="I29" s="20"/>
       <c r="J29" s="20"/>
@@ -1937,7 +1989,7 @@
       </c>
       <c r="D30" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>48</v>
@@ -1945,7 +1997,9 @@
       <c r="F30" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="20"/>
+      <c r="G30" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H30" s="20"/>
       <c r="I30" s="20"/>
       <c r="J30" s="20"/>
@@ -1977,7 +2031,7 @@
       </c>
       <c r="D31" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>47</v>
@@ -1985,7 +2039,9 @@
       <c r="F31" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G31" s="20"/>
+      <c r="G31" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
       <c r="J31" s="20"/>

--- a/TFD 3-1/Regular Assessment TFD 3-1.xlsx
+++ b/TFD 3-1/Regular Assessment TFD 3-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4D97D4-27F7-4FCD-AE88-12A70D6F83D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AC439A-22DD-42AB-A77A-68698A9D2577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -413,7 +413,37 @@
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2066,11 +2096,15 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+      <formula>0.6</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="between">
+      <formula>0.6</formula>
+      <formula>0.89</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TFD 3-1/Regular Assessment TFD 3-1.xlsx
+++ b/TFD 3-1/Regular Assessment TFD 3-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AC439A-22DD-42AB-A77A-68698A9D2577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AEBE1B-076A-4CF1-A959-E334736899EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TFD 3-1 Attendance'!$A$3:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TFD 3-1 Attendance'!$A$3:$F$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="51">
   <si>
     <t>SL</t>
   </si>
@@ -189,6 +211,9 @@
   </si>
   <si>
     <t>TFD 3-1</t>
+  </si>
+  <si>
+    <t>Marks</t>
   </si>
 </sst>
 </file>
@@ -342,7 +367,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -402,6 +427,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -413,7 +439,37 @@
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -441,26 +497,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -740,29 +776,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.77734375" style="18" customWidth="1"/>
-    <col min="7" max="7" width="35.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="18"/>
+    <col min="5" max="5" width="12" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.77734375" style="18" customWidth="1"/>
+    <col min="8" max="8" width="35.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="25" width="20.77734375" style="18" customWidth="1"/>
+    <col min="26" max="16384" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.5">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.5">
+      <c r="A1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="21"/>
+      <c r="B1" s="22"/>
       <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
       <c r="D1" s="7"/>
-      <c r="E1" s="8"/>
+      <c r="E1" s="7"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
@@ -782,8 +821,9 @@
       <c r="V1" s="8"/>
       <c r="W1" s="8"/>
       <c r="X1" s="8"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y1" s="8"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -795,87 +835,88 @@
         <v>36</v>
       </c>
       <c r="D2" s="7"/>
-      <c r="E2" s="9">
+      <c r="E2" s="7"/>
+      <c r="F2" s="9">
         <v>1</v>
       </c>
-      <c r="F2" s="9">
-        <f>E2+1</f>
+      <c r="G2" s="9">
+        <f>F2+1</f>
         <v>2</v>
       </c>
-      <c r="G2" s="9">
-        <f t="shared" ref="G2:X2" si="0">F2+1</f>
+      <c r="H2" s="9">
+        <f t="shared" ref="H2:Y2" si="0">G2+1</f>
         <v>3</v>
       </c>
-      <c r="H2" s="9">
+      <c r="I2" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I2" s="9">
+      <c r="J2" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J2" s="9">
+      <c r="K2" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K2" s="9">
+      <c r="L2" s="9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="L2" s="9">
+      <c r="M2" s="9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="M2" s="9">
+      <c r="N2" s="9">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="N2" s="9">
+      <c r="O2" s="9">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O2" s="9">
+      <c r="P2" s="9">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="P2" s="9">
+      <c r="Q2" s="9">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="R2" s="9">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="R2" s="9">
+      <c r="S2" s="9">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="S2" s="9">
+      <c r="T2" s="9">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="T2" s="9">
+      <c r="U2" s="9">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U2" s="9">
+      <c r="V2" s="9">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="V2" s="9">
+      <c r="W2" s="9">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="W2" s="9">
+      <c r="X2" s="9">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="X2" s="9">
+      <c r="Y2" s="9">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -888,17 +929,21 @@
       <c r="D3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="5">
         <v>46267</v>
       </c>
-      <c r="F3" s="5">
+      <c r="G3" s="5">
         <v>46271</v>
       </c>
-      <c r="G3" s="5">
+      <c r="H3" s="5">
         <v>46274</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+      <c r="I3" s="5">
+        <v>46278</v>
+      </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
@@ -914,8 +959,9 @@
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y3" s="5"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -926,20 +972,25 @@
         <v>3</v>
       </c>
       <c r="D4" s="10">
-        <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
+        <f t="shared" ref="D4:D31" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="20" t="s">
+      <c r="E4" s="1" cm="1">
+        <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
+      <c r="H4" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J4" s="20"/>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
@@ -955,8 +1006,9 @@
       <c r="V4" s="20"/>
       <c r="W4" s="20"/>
       <c r="X4" s="20"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y4" s="20"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A5" s="1">
         <f>A4+1</f>
         <v>2</v>
@@ -968,20 +1020,25 @@
         <v>4</v>
       </c>
       <c r="D5" s="10">
-        <f t="shared" ref="D5:D31" si="1">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="20" t="s">
+      <c r="E5" s="1" cm="1">
+        <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
+      <c r="H5" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J5" s="20"/>
       <c r="K5" s="20"/>
       <c r="L5" s="20"/>
@@ -997,8 +1054,9 @@
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
       <c r="X5" s="20"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y5" s="20"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A31" si="2">A5+1</f>
         <v>3</v>
@@ -1013,17 +1071,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="20" t="s">
+      <c r="E6" s="1" cm="1">
+        <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
+      <c r="H6" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J6" s="20"/>
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
@@ -1039,8 +1102,9 @@
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
       <c r="X6" s="20"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y6" s="20"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -1055,17 +1119,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="20" t="s">
+      <c r="E7" s="1" cm="1">
+        <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
+      <c r="H7" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J7" s="20"/>
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
@@ -1081,8 +1150,9 @@
       <c r="V7" s="20"/>
       <c r="W7" s="20"/>
       <c r="X7" s="20"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y7" s="20"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -1097,17 +1167,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="20" t="s">
+      <c r="E8" s="1" cm="1">
+        <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
+      <c r="H8" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J8" s="20"/>
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
@@ -1123,8 +1198,9 @@
       <c r="V8" s="20"/>
       <c r="W8" s="20"/>
       <c r="X8" s="20"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y8" s="20"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -1139,17 +1215,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="20" t="s">
+      <c r="E9" s="1" cm="1">
+        <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
+      <c r="H9" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J9" s="20"/>
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
@@ -1165,8 +1246,9 @@
       <c r="V9" s="20"/>
       <c r="W9" s="20"/>
       <c r="X9" s="20"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y9" s="20"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A10" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -1179,19 +1261,24 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>47</v>
+        <v>0.25</v>
+      </c>
+      <c r="E10" s="1" cm="1">
+        <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
+      <c r="H10" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="J10" s="20"/>
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
@@ -1207,8 +1294,9 @@
       <c r="V10" s="20"/>
       <c r="W10" s="20"/>
       <c r="X10" s="20"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y10" s="20"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A11" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -1223,17 +1311,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="20" t="s">
+      <c r="E11" s="1" cm="1">
+        <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
+      <c r="H11" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
       <c r="L11" s="20"/>
@@ -1249,8 +1342,9 @@
       <c r="V11" s="20"/>
       <c r="W11" s="20"/>
       <c r="X11" s="20"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y11" s="20"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -1265,17 +1359,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="20" t="s">
+      <c r="E12" s="1" cm="1">
+        <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,7.5,D12&gt;=80%,6,D12&gt;=70%,4.5,D12&gt;=60%,3,D12&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
+      <c r="H12" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J12" s="20"/>
       <c r="K12" s="20"/>
       <c r="L12" s="20"/>
@@ -1291,8 +1390,9 @@
       <c r="V12" s="20"/>
       <c r="W12" s="20"/>
       <c r="X12" s="20"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y12" s="20"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -1305,19 +1405,24 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="17" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="E13" s="1" cm="1">
+        <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
+      <c r="H13" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J13" s="20"/>
       <c r="K13" s="20"/>
       <c r="L13" s="20"/>
@@ -1333,8 +1438,9 @@
       <c r="V13" s="20"/>
       <c r="W13" s="20"/>
       <c r="X13" s="20"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y13" s="20"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -1349,17 +1455,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="20" t="s">
+      <c r="E14" s="1" cm="1">
+        <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
+      <c r="H14" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J14" s="20"/>
       <c r="K14" s="20"/>
       <c r="L14" s="20"/>
@@ -1375,8 +1486,9 @@
       <c r="V14" s="20"/>
       <c r="W14" s="20"/>
       <c r="X14" s="20"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y14" s="20"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -1389,19 +1501,24 @@
       </c>
       <c r="D15" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="17" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="E15" s="1" cm="1">
+        <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
+      <c r="I15" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J15" s="20"/>
       <c r="K15" s="20"/>
       <c r="L15" s="20"/>
@@ -1417,8 +1534,9 @@
       <c r="V15" s="20"/>
       <c r="W15" s="20"/>
       <c r="X15" s="20"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y15" s="20"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -1431,19 +1549,24 @@
       </c>
       <c r="D16" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E16" s="17" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="E16" s="1" cm="1">
+        <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F16" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="G16" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
+      <c r="H16" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J16" s="20"/>
       <c r="K16" s="20"/>
       <c r="L16" s="20"/>
@@ -1459,8 +1582,9 @@
       <c r="V16" s="20"/>
       <c r="W16" s="20"/>
       <c r="X16" s="20"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y16" s="20"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -1473,19 +1597,24 @@
       </c>
       <c r="D17" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="17" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="E17" s="1" cm="1">
+        <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
+      <c r="H17" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J17" s="20"/>
       <c r="K17" s="20"/>
       <c r="L17" s="20"/>
@@ -1501,8 +1630,9 @@
       <c r="V17" s="20"/>
       <c r="W17" s="20"/>
       <c r="X17" s="20"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y17" s="20"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1515,19 +1645,24 @@
       </c>
       <c r="D18" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="17" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="E18" s="1" cm="1">
+        <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
+      <c r="H18" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J18" s="20"/>
       <c r="K18" s="20"/>
       <c r="L18" s="20"/>
@@ -1543,8 +1678,9 @@
       <c r="V18" s="20"/>
       <c r="W18" s="20"/>
       <c r="X18" s="20"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y18" s="20"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -1557,19 +1693,24 @@
       </c>
       <c r="D19" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="20" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="E19" s="1" cm="1">
+        <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
+      <c r="H19" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="J19" s="20"/>
       <c r="K19" s="20"/>
       <c r="L19" s="20"/>
@@ -1585,8 +1726,9 @@
       <c r="V19" s="20"/>
       <c r="W19" s="20"/>
       <c r="X19" s="20"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y19" s="20"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -1601,17 +1743,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="20" t="s">
+      <c r="E20" s="1" cm="1">
+        <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
+      <c r="H20" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J20" s="20"/>
       <c r="K20" s="20"/>
       <c r="L20" s="20"/>
@@ -1627,8 +1774,9 @@
       <c r="V20" s="20"/>
       <c r="W20" s="20"/>
       <c r="X20" s="20"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y20" s="20"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -1643,17 +1791,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="20" t="s">
+      <c r="E21" s="1" cm="1">
+        <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
+      <c r="H21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J21" s="20"/>
       <c r="K21" s="20"/>
       <c r="L21" s="20"/>
@@ -1669,8 +1822,9 @@
       <c r="V21" s="20"/>
       <c r="W21" s="20"/>
       <c r="X21" s="20"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y21" s="20"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -1683,19 +1837,24 @@
       </c>
       <c r="D22" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="17" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="E22" s="1" cm="1">
+        <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
+      <c r="H22" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J22" s="20"/>
       <c r="K22" s="20"/>
       <c r="L22" s="20"/>
@@ -1711,8 +1870,9 @@
       <c r="V22" s="20"/>
       <c r="W22" s="20"/>
       <c r="X22" s="20"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y22" s="20"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -1727,17 +1887,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="20" t="s">
+      <c r="E23" s="1" cm="1">
+        <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
+      <c r="H23" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J23" s="20"/>
       <c r="K23" s="20"/>
       <c r="L23" s="20"/>
@@ -1753,8 +1918,9 @@
       <c r="V23" s="20"/>
       <c r="W23" s="20"/>
       <c r="X23" s="20"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y23" s="20"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -1769,17 +1935,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="20" t="s">
+      <c r="E24" s="1" cm="1">
+        <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G24" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
+      <c r="H24" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J24" s="20"/>
       <c r="K24" s="20"/>
       <c r="L24" s="20"/>
@@ -1795,8 +1966,9 @@
       <c r="V24" s="20"/>
       <c r="W24" s="20"/>
       <c r="X24" s="20"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y24" s="20"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -1811,17 +1983,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="20" t="s">
+      <c r="E25" s="1" cm="1">
+        <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
+      <c r="H25" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J25" s="20"/>
       <c r="K25" s="20"/>
       <c r="L25" s="20"/>
@@ -1837,8 +2014,9 @@
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
       <c r="X25" s="20"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y25" s="20"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -1853,17 +2031,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="20" t="s">
+      <c r="E26" s="1" cm="1">
+        <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G26" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
+      <c r="H26" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J26" s="20"/>
       <c r="K26" s="20"/>
       <c r="L26" s="20"/>
@@ -1879,8 +2062,9 @@
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
       <c r="X26" s="20"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -1895,17 +2079,22 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="20" t="s">
+      <c r="E27" s="1" cm="1">
+        <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G27" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
+      <c r="H27" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J27" s="20"/>
       <c r="K27" s="20"/>
       <c r="L27" s="20"/>
@@ -1921,8 +2110,9 @@
       <c r="V27" s="20"/>
       <c r="W27" s="20"/>
       <c r="X27" s="20"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -1935,19 +2125,24 @@
       </c>
       <c r="D28" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E28" s="17" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="1" cm="1">
+        <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F28" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="G28" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
+      <c r="H28" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I28" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J28" s="20"/>
       <c r="K28" s="20"/>
       <c r="L28" s="20"/>
@@ -1963,8 +2158,9 @@
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
       <c r="X28" s="20"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -1977,19 +2173,24 @@
       </c>
       <c r="D29" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" s="20" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="E29" s="1" cm="1">
+        <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G29" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
+      <c r="H29" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I29" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="J29" s="20"/>
       <c r="K29" s="20"/>
       <c r="L29" s="20"/>
@@ -2005,8 +2206,9 @@
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
       <c r="X29" s="20"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -2019,19 +2221,24 @@
       </c>
       <c r="D30" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" s="17" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="E30" s="1" cm="1">
+        <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
+      <c r="H30" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I30" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J30" s="20"/>
       <c r="K30" s="20"/>
       <c r="L30" s="20"/>
@@ -2047,8 +2254,9 @@
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
       <c r="X30" s="20"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.5">
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -2061,19 +2269,24 @@
       </c>
       <c r="D31" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E31" s="17" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="E31" s="1" cm="1">
+        <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F31" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="G31" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
+      <c r="H31" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="J31" s="20"/>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
@@ -2089,22 +2302,35 @@
       <c r="V31" s="20"/>
       <c r="W31" s="20"/>
       <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:F31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
       <formula>0.6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="between">
       <formula>0.6</formula>
       <formula>0.89</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E31">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>2</formula>
+      <formula>5.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2127,10 +2353,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="21"/>
+      <c r="B1" s="22"/>
       <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
@@ -2146,10 +2372,10 @@
       <c r="G1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="22"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -2168,8 +2394,8 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/TFD 3-1/Regular Assessment TFD 3-1.xlsx
+++ b/TFD 3-1/Regular Assessment TFD 3-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AEBE1B-076A-4CF1-A959-E334736899EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCAC023-5210-4FB5-AACE-B604CB6CA1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="51">
   <si>
     <t>SL</t>
   </si>
@@ -787,8 +787,9 @@
     <col min="6" max="6" width="39.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.77734375" style="18" customWidth="1"/>
     <col min="8" max="8" width="35.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.33203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="25" width="20.77734375" style="18" customWidth="1"/>
+    <col min="9" max="9" width="32.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="25" width="20.77734375" style="18" customWidth="1"/>
     <col min="26" max="16384" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
@@ -944,7 +945,9 @@
       <c r="I3" s="5">
         <v>46278</v>
       </c>
-      <c r="J3" s="5"/>
+      <c r="J3" s="5">
+        <v>46281</v>
+      </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -991,7 +994,9 @@
       <c r="I4" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="20"/>
+      <c r="J4" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
       <c r="M4" s="20"/>
@@ -1039,7 +1044,9 @@
       <c r="I5" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J5" s="20"/>
+      <c r="J5" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K5" s="20"/>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
@@ -1087,7 +1094,9 @@
       <c r="I6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="20"/>
+      <c r="J6" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
@@ -1135,7 +1144,9 @@
       <c r="I7" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="20"/>
+      <c r="J7" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="20"/>
@@ -1183,7 +1194,9 @@
       <c r="I8" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="20"/>
+      <c r="J8" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
@@ -1231,7 +1244,9 @@
       <c r="I9" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="20"/>
+      <c r="J9" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
@@ -1261,7 +1276,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1279,7 +1294,9 @@
       <c r="I10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="20"/>
+      <c r="J10" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
       <c r="M10" s="20"/>
@@ -1327,7 +1344,9 @@
       <c r="I11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="20"/>
+      <c r="J11" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K11" s="20"/>
       <c r="L11" s="20"/>
       <c r="M11" s="20"/>
@@ -1345,7 +1364,7 @@
       <c r="Y11" s="20"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.5">
-      <c r="A12" s="1">
+      <c r="A12" s="12">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
@@ -1375,7 +1394,9 @@
       <c r="I12" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="20"/>
+      <c r="J12" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K12" s="20"/>
       <c r="L12" s="20"/>
       <c r="M12" s="20"/>
@@ -1405,11 +1426,11 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E13" s="1" cm="1">
         <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>48</v>
@@ -1423,7 +1444,9 @@
       <c r="I13" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J13" s="20"/>
+      <c r="J13" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K13" s="20"/>
       <c r="L13" s="20"/>
       <c r="M13" s="20"/>
@@ -1471,7 +1494,9 @@
       <c r="I14" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J14" s="20"/>
+      <c r="J14" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K14" s="20"/>
       <c r="L14" s="20"/>
       <c r="M14" s="20"/>
@@ -1501,11 +1526,11 @@
       </c>
       <c r="D15" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E15" s="1" cm="1">
         <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>48</v>
@@ -1519,7 +1544,9 @@
       <c r="I15" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J15" s="20"/>
+      <c r="J15" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K15" s="20"/>
       <c r="L15" s="20"/>
       <c r="M15" s="20"/>
@@ -1549,11 +1576,11 @@
       </c>
       <c r="D16" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E16" s="1" cm="1">
         <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>47</v>
@@ -1567,7 +1594,9 @@
       <c r="I16" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J16" s="20"/>
+      <c r="J16" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K16" s="20"/>
       <c r="L16" s="20"/>
       <c r="M16" s="20"/>
@@ -1597,11 +1626,11 @@
       </c>
       <c r="D17" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>48</v>
@@ -1615,7 +1644,9 @@
       <c r="I17" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J17" s="20"/>
+      <c r="J17" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K17" s="20"/>
       <c r="L17" s="20"/>
       <c r="M17" s="20"/>
@@ -1645,11 +1676,11 @@
       </c>
       <c r="D18" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E18" s="1" cm="1">
         <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>48</v>
@@ -1663,7 +1694,9 @@
       <c r="I18" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J18" s="20"/>
+      <c r="J18" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K18" s="20"/>
       <c r="L18" s="20"/>
       <c r="M18" s="20"/>
@@ -1693,11 +1726,11 @@
       </c>
       <c r="D19" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>48</v>
@@ -1711,7 +1744,9 @@
       <c r="I19" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="J19" s="20"/>
+      <c r="J19" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="K19" s="20"/>
       <c r="L19" s="20"/>
       <c r="M19" s="20"/>
@@ -1759,7 +1794,9 @@
       <c r="I20" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J20" s="20"/>
+      <c r="J20" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K20" s="20"/>
       <c r="L20" s="20"/>
       <c r="M20" s="20"/>
@@ -1807,7 +1844,9 @@
       <c r="I21" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J21" s="20"/>
+      <c r="J21" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K21" s="20"/>
       <c r="L21" s="20"/>
       <c r="M21" s="20"/>
@@ -1837,11 +1876,11 @@
       </c>
       <c r="D22" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E22" s="1" cm="1">
         <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>48</v>
@@ -1855,7 +1894,9 @@
       <c r="I22" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J22" s="20"/>
+      <c r="J22" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K22" s="20"/>
       <c r="L22" s="20"/>
       <c r="M22" s="20"/>
@@ -1903,7 +1944,9 @@
       <c r="I23" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J23" s="20"/>
+      <c r="J23" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K23" s="20"/>
       <c r="L23" s="20"/>
       <c r="M23" s="20"/>
@@ -1951,7 +1994,9 @@
       <c r="I24" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J24" s="20"/>
+      <c r="J24" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K24" s="20"/>
       <c r="L24" s="20"/>
       <c r="M24" s="20"/>
@@ -1981,11 +2026,11 @@
       </c>
       <c r="D25" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>48</v>
@@ -1999,7 +2044,9 @@
       <c r="I25" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J25" s="20"/>
+      <c r="J25" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="K25" s="20"/>
       <c r="L25" s="20"/>
       <c r="M25" s="20"/>
@@ -2047,7 +2094,9 @@
       <c r="I26" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J26" s="20"/>
+      <c r="J26" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K26" s="20"/>
       <c r="L26" s="20"/>
       <c r="M26" s="20"/>
@@ -2095,7 +2144,9 @@
       <c r="I27" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J27" s="20"/>
+      <c r="J27" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K27" s="20"/>
       <c r="L27" s="20"/>
       <c r="M27" s="20"/>
@@ -2125,11 +2176,11 @@
       </c>
       <c r="D28" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E28" s="1" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>47</v>
@@ -2143,7 +2194,9 @@
       <c r="I28" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J28" s="20"/>
+      <c r="J28" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K28" s="20"/>
       <c r="L28" s="20"/>
       <c r="M28" s="20"/>
@@ -2173,11 +2226,11 @@
       </c>
       <c r="D29" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="E29" s="1" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>48</v>
@@ -2191,7 +2244,9 @@
       <c r="I29" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="J29" s="20"/>
+      <c r="J29" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="K29" s="20"/>
       <c r="L29" s="20"/>
       <c r="M29" s="20"/>
@@ -2221,11 +2276,11 @@
       </c>
       <c r="D30" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E30" s="1" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>48</v>
@@ -2239,7 +2294,9 @@
       <c r="I30" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J30" s="20"/>
+      <c r="J30" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K30" s="20"/>
       <c r="L30" s="20"/>
       <c r="M30" s="20"/>
@@ -2269,11 +2326,11 @@
       </c>
       <c r="D31" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E31" s="1" cm="1">
         <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>47</v>
@@ -2287,7 +2344,9 @@
       <c r="I31" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J31" s="20"/>
+      <c r="J31" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
       <c r="M31" s="20"/>

--- a/TFD 3-1/Regular Assessment TFD 3-1.xlsx
+++ b/TFD 3-1/Regular Assessment TFD 3-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCAC023-5210-4FB5-AACE-B604CB6CA1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6967DB-26D1-4683-B233-0C60B7383FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TFD 3-1 Attendance'!$A$3:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TFD 3-1 Attendance'!$A$3:$F$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="51">
   <si>
     <t>SL</t>
   </si>
@@ -223,7 +223,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,8 +277,14 @@
       <name val="Gill Sans MT"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="3" tint="-0.249977111117893"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,6 +344,18 @@
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -367,7 +385,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -428,10 +446,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -776,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="11" bestFit="1" customWidth="1"/>
@@ -789,15 +813,16 @@
     <col min="8" max="8" width="35.6640625" style="18" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="32.44140625" style="18" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="37.33203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="25" width="20.77734375" style="18" customWidth="1"/>
+    <col min="11" max="12" width="34.88671875" style="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="25" width="30.5546875" style="18" customWidth="1"/>
     <col min="26" max="16384" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.5">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="23"/>
       <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
@@ -829,8 +854,8 @@
         <v>35</v>
       </c>
       <c r="B2" s="7">
-        <f>COUNT(A4:A31)</f>
-        <v>28</v>
+        <f>COUNT(A4:A30)</f>
+        <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>36</v>
@@ -948,8 +973,12 @@
       <c r="J3" s="5">
         <v>46281</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5">
+        <v>46289</v>
+      </c>
+      <c r="L3" s="5">
+        <v>46289</v>
+      </c>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
@@ -975,7 +1004,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="10">
-        <f t="shared" ref="D4:D31" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
+        <f t="shared" ref="D4:D30" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
         <v>1</v>
       </c>
       <c r="E4" s="1" cm="1">
@@ -997,8 +1026,12 @@
       <c r="J4" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
+      <c r="K4" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M4" s="20"/>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
@@ -1047,8 +1080,12 @@
       <c r="J5" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
+      <c r="K5" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
       <c r="O5" s="20"/>
@@ -1065,7 +1102,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.5">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A31" si="2">A5+1</f>
+        <f t="shared" ref="A6:A30" si="2">A5+1</f>
         <v>3</v>
       </c>
       <c r="B6" s="1">
@@ -1097,8 +1134,12 @@
       <c r="J6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
+      <c r="K6" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
       <c r="O6" s="20"/>
@@ -1147,8 +1188,12 @@
       <c r="J7" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
+      <c r="K7" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
       <c r="O7" s="20"/>
@@ -1197,8 +1242,12 @@
       <c r="J8" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
+      <c r="K8" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
       <c r="O8" s="20"/>
@@ -1247,8 +1296,12 @@
       <c r="J9" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
+      <c r="K9" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
       <c r="O9" s="20"/>
@@ -1264,7 +1317,7 @@
       <c r="Y9" s="20"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.5">
-      <c r="A10" s="1">
+      <c r="A10" s="22">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -1276,7 +1329,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1297,8 +1350,12 @@
       <c r="J10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
+      <c r="K10" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M10" s="20"/>
       <c r="N10" s="20"/>
       <c r="O10" s="20"/>
@@ -1347,8 +1404,12 @@
       <c r="J11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
+      <c r="K11" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M11" s="20"/>
       <c r="N11" s="20"/>
       <c r="O11" s="20"/>
@@ -1364,7 +1425,7 @@
       <c r="Y11" s="20"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.5">
-      <c r="A12" s="12">
+      <c r="A12" s="25">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
@@ -1397,8 +1458,12 @@
       <c r="J12" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
+      <c r="K12" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
       <c r="O12" s="20"/>
@@ -1426,7 +1491,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E13" s="1" cm="1">
         <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
@@ -1447,8 +1512,12 @@
       <c r="J13" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
+      <c r="K13" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M13" s="20"/>
       <c r="N13" s="20"/>
       <c r="O13" s="20"/>
@@ -1497,8 +1566,12 @@
       <c r="J14" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="K14" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M14" s="20"/>
       <c r="N14" s="20"/>
       <c r="O14" s="20"/>
@@ -1526,7 +1599,7 @@
       </c>
       <c r="D15" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E15" s="1" cm="1">
         <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
@@ -1547,8 +1620,12 @@
       <c r="J15" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
+      <c r="K15" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M15" s="20"/>
       <c r="N15" s="20"/>
       <c r="O15" s="20"/>
@@ -1576,7 +1653,7 @@
       </c>
       <c r="D16" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E16" s="1" cm="1">
         <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
@@ -1597,8 +1674,12 @@
       <c r="J16" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="K16" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M16" s="20"/>
       <c r="N16" s="20"/>
       <c r="O16" s="20"/>
@@ -1626,7 +1707,7 @@
       </c>
       <c r="D17" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
@@ -1647,8 +1728,12 @@
       <c r="J17" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="K17" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
       <c r="O17" s="20"/>
@@ -1676,7 +1761,7 @@
       </c>
       <c r="D18" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E18" s="1" cm="1">
         <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
@@ -1697,8 +1782,12 @@
       <c r="J18" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
+      <c r="K18" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M18" s="20"/>
       <c r="N18" s="20"/>
       <c r="O18" s="20"/>
@@ -1726,11 +1815,11 @@
       </c>
       <c r="D19" s="10">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>48</v>
@@ -1747,8 +1836,12 @@
       <c r="J19" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="K19" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
       <c r="O19" s="20"/>
@@ -1797,8 +1890,12 @@
       <c r="J20" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="K20" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M20" s="20"/>
       <c r="N20" s="20"/>
       <c r="O20" s="20"/>
@@ -1847,8 +1944,12 @@
       <c r="J21" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
+      <c r="K21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M21" s="20"/>
       <c r="N21" s="20"/>
       <c r="O21" s="20"/>
@@ -1876,7 +1977,7 @@
       </c>
       <c r="D22" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E22" s="1" cm="1">
         <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
@@ -1897,8 +1998,12 @@
       <c r="J22" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
+      <c r="K22" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M22" s="20"/>
       <c r="N22" s="20"/>
       <c r="O22" s="20"/>
@@ -1947,8 +2052,12 @@
       <c r="J23" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="K23" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M23" s="20"/>
       <c r="N23" s="20"/>
       <c r="O23" s="20"/>
@@ -1997,8 +2106,12 @@
       <c r="J24" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
+      <c r="K24" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M24" s="20"/>
       <c r="N24" s="20"/>
       <c r="O24" s="20"/>
@@ -2026,7 +2139,7 @@
       </c>
       <c r="D25" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
@@ -2047,8 +2160,12 @@
       <c r="J25" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
+      <c r="K25" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M25" s="20"/>
       <c r="N25" s="20"/>
       <c r="O25" s="20"/>
@@ -2097,8 +2214,12 @@
       <c r="J26" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+      <c r="K26" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M26" s="20"/>
       <c r="N26" s="20"/>
       <c r="O26" s="20"/>
@@ -2119,21 +2240,21 @@
         <v>24</v>
       </c>
       <c r="B27" s="1">
-        <v>23010601014</v>
+        <v>23010601015</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E27" s="1" cm="1">
         <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
-        <v>7.5</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>48</v>
+        <v>6</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>47</v>
       </c>
       <c r="G27" s="20" t="s">
         <v>48</v>
@@ -2147,8 +2268,12 @@
       <c r="J27" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
+      <c r="K27" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M27" s="20"/>
       <c r="N27" s="20"/>
       <c r="O27" s="20"/>
@@ -2169,36 +2294,40 @@
         <v>25</v>
       </c>
       <c r="B28" s="1">
-        <v>23010601015</v>
+        <v>23010601024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E28" s="1" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
-        <v>6</v>
-      </c>
-      <c r="F28" s="17" t="s">
+        <v>4.5</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I28" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="H28" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="I28" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="J28" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
+      <c r="J28" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M28" s="20"/>
       <c r="N28" s="20"/>
       <c r="O28" s="20"/>
@@ -2218,37 +2347,41 @@
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="B29" s="1">
-        <v>23010601024</v>
+      <c r="B29" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E29" s="1" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G29" s="20" t="s">
-        <v>48</v>
+      <c r="G29" s="17" t="s">
+        <v>47</v>
       </c>
       <c r="H29" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="I29" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="J29" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
+      <c r="I29" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
       <c r="O29" s="20"/>
@@ -2269,25 +2402,25 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E30" s="1" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
         <v>6</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G30" s="17" t="s">
+      <c r="F30" s="17" t="s">
         <v>47</v>
       </c>
+      <c r="G30" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="H30" s="20" t="s">
         <v>48</v>
       </c>
@@ -2297,8 +2430,12 @@
       <c r="J30" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
+      <c r="K30" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>48</v>
+      </c>
       <c r="M30" s="20"/>
       <c r="N30" s="20"/>
       <c r="O30" s="20"/>
@@ -2313,62 +2450,12 @@
       <c r="X30" s="20"/>
       <c r="Y30" s="20"/>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.5">
-      <c r="A31" s="1">
-        <f t="shared" si="2"/>
-        <v>28</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="10">
-        <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="E31" s="1" cm="1">
-        <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
-        <v>6</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="H31" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="I31" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="J31" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="U31" s="20"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="20"/>
-      <c r="X31" s="20"/>
-      <c r="Y31" s="20"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:F31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:F30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D31">
+  <conditionalFormatting sqref="D4:D30">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
       <formula>0.6</formula>
     </cfRule>
@@ -2380,7 +2467,7 @@
       <formula>0.89</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E31">
+  <conditionalFormatting sqref="E4:E30">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>3</formula>
     </cfRule>
@@ -2412,10 +2499,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="23"/>
       <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
@@ -2431,10 +2518,10 @@
       <c r="G1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="23"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -2453,8 +2540,8 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/TFD 3-1/Regular Assessment TFD 3-1.xlsx
+++ b/TFD 3-1/Regular Assessment TFD 3-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF9D701-FEC2-4D3E-AB00-0BFBE5E72E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2675E9CE-C9E1-448B-9663-A295C476D7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="832" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TFD 3-1 Attendance" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="54">
   <si>
     <t>SL</t>
   </si>
@@ -203,15 +203,6 @@
   </si>
   <si>
     <t>Drawing Not Clear</t>
-  </si>
-  <si>
-    <t>Meet</t>
-  </si>
-  <si>
-    <t>Not Submitted</t>
-  </si>
-  <si>
-    <t>Drew 3 Figures</t>
   </si>
   <si>
     <t>Class Test</t>
@@ -313,7 +304,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -376,12 +367,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,16 +509,16 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -545,16 +530,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -625,6 +610,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF7C80"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1058,7 +1048,9 @@
       <c r="M3" s="3">
         <v>46292</v>
       </c>
-      <c r="N3" s="3"/>
+      <c r="N3" s="3">
+        <v>46295</v>
+      </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
@@ -1108,7 +1100,9 @@
       <c r="M4" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="15"/>
+      <c r="N4" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
@@ -1159,7 +1153,9 @@
       <c r="M5" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="15"/>
+      <c r="N5" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
       <c r="Q5" s="15"/>
@@ -1210,7 +1206,9 @@
       <c r="M6" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="15"/>
+      <c r="N6" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
       <c r="Q6" s="15"/>
@@ -1231,11 +1229,11 @@
       </c>
       <c r="D7" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E7" s="1" cm="1">
         <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>40</v>
@@ -1261,7 +1259,9 @@
       <c r="M7" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="15"/>
+      <c r="N7" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
       <c r="Q7" s="15"/>
@@ -1282,11 +1282,11 @@
       </c>
       <c r="D8" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E8" s="1" cm="1">
         <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>40</v>
@@ -1312,7 +1312,9 @@
       <c r="M8" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N8" s="15"/>
+      <c r="N8" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
       <c r="Q8" s="15"/>
@@ -1363,7 +1365,9 @@
       <c r="M9" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N9" s="15"/>
+      <c r="N9" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
       <c r="Q9" s="15"/>
@@ -1384,7 +1388,7 @@
       </c>
       <c r="D10" s="7">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1414,7 +1418,9 @@
       <c r="M10" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N10" s="15"/>
+      <c r="N10" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
       <c r="Q10" s="15"/>
@@ -1465,7 +1471,9 @@
       <c r="M11" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N11" s="15"/>
+      <c r="N11" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
       <c r="Q11" s="15"/>
@@ -1516,7 +1524,9 @@
       <c r="M12" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N12" s="15"/>
+      <c r="N12" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O12" s="15"/>
       <c r="P12" s="15"/>
       <c r="Q12" s="15"/>
@@ -1537,7 +1547,7 @@
       </c>
       <c r="D13" s="7">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E13" s="1" cm="1">
         <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
@@ -1567,7 +1577,9 @@
       <c r="M13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="N13" s="15"/>
+      <c r="N13" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
       <c r="Q13" s="15"/>
@@ -1618,7 +1630,9 @@
       <c r="M14" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N14" s="15"/>
+      <c r="N14" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
       <c r="Q14" s="15"/>
@@ -1639,7 +1653,7 @@
       </c>
       <c r="D15" s="7">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E15" s="1" cm="1">
         <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
@@ -1669,7 +1683,9 @@
       <c r="M15" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N15" s="15"/>
+      <c r="N15" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="15"/>
@@ -1690,7 +1706,7 @@
       </c>
       <c r="D16" s="7">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E16" s="1" cm="1">
         <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
@@ -1720,7 +1736,9 @@
       <c r="M16" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N16" s="15"/>
+      <c r="N16" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O16" s="15"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="15"/>
@@ -1741,11 +1759,11 @@
       </c>
       <c r="D17" s="7">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>40</v>
@@ -1771,7 +1789,9 @@
       <c r="M17" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="15"/>
+      <c r="N17" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="15"/>
@@ -1792,7 +1812,7 @@
       </c>
       <c r="D18" s="7">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E18" s="1" cm="1">
         <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
@@ -1822,7 +1842,9 @@
       <c r="M18" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N18" s="15"/>
+      <c r="N18" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O18" s="15"/>
       <c r="P18" s="15"/>
       <c r="Q18" s="15"/>
@@ -1843,7 +1865,7 @@
       </c>
       <c r="D19" s="7">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
@@ -1873,7 +1895,9 @@
       <c r="M19" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="N19" s="15"/>
+      <c r="N19" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O19" s="15"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="15"/>
@@ -1924,7 +1948,9 @@
       <c r="M20" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N20" s="15"/>
+      <c r="N20" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
       <c r="Q20" s="15"/>
@@ -1975,7 +2001,9 @@
       <c r="M21" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N21" s="15"/>
+      <c r="N21" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O21" s="15"/>
       <c r="P21" s="15"/>
       <c r="Q21" s="15"/>
@@ -1996,7 +2024,7 @@
       </c>
       <c r="D22" s="7">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E22" s="1" cm="1">
         <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
@@ -2026,7 +2054,9 @@
       <c r="M22" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N22" s="15"/>
+      <c r="N22" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
       <c r="Q22" s="15"/>
@@ -2077,7 +2107,9 @@
       <c r="M23" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N23" s="15"/>
+      <c r="N23" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
       <c r="Q23" s="15"/>
@@ -2098,11 +2130,11 @@
       </c>
       <c r="D24" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>40</v>
@@ -2128,7 +2160,9 @@
       <c r="M24" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N24" s="15"/>
+      <c r="N24" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="15"/>
@@ -2149,11 +2183,11 @@
       </c>
       <c r="D25" s="7">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>40</v>
@@ -2179,7 +2213,9 @@
       <c r="M25" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N25" s="15"/>
+      <c r="N25" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
@@ -2230,7 +2266,9 @@
       <c r="M26" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N26" s="15"/>
+      <c r="N26" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
       <c r="Q26" s="15"/>
@@ -2251,7 +2289,7 @@
       </c>
       <c r="D27" s="7">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E27" s="1" cm="1">
         <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
@@ -2281,7 +2319,9 @@
       <c r="M27" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N27" s="15"/>
+      <c r="N27" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
       <c r="Q27" s="15"/>
@@ -2302,7 +2342,7 @@
       </c>
       <c r="D28" s="7">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E28" s="1" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
@@ -2332,7 +2372,9 @@
       <c r="M28" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="15"/>
+      <c r="N28" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
@@ -2353,7 +2395,7 @@
       </c>
       <c r="D29" s="7">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E29" s="1" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
@@ -2383,7 +2425,9 @@
       <c r="M29" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N29" s="15"/>
+      <c r="N29" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O29" s="15"/>
       <c r="P29" s="15"/>
       <c r="Q29" s="15"/>
@@ -2404,7 +2448,7 @@
       </c>
       <c r="D30" s="7">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E30" s="1" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
@@ -2434,7 +2478,9 @@
       <c r="M30" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N30" s="15"/>
+      <c r="N30" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
@@ -2507,7 +2553,7 @@
         <v>36</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F1" s="26" t="s">
         <v>37</v>
@@ -2529,13 +2575,13 @@
         <v>27</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>38</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F2" s="26"/>
       <c r="G2" s="26"/>
@@ -2723,7 +2769,7 @@
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="22">
+      <c r="A10" s="21">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -2749,7 +2795,7 @@
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="22">
+      <c r="A11" s="21">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -2775,7 +2821,7 @@
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="23">
+      <c r="A12" s="22">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
@@ -2863,19 +2909,19 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="21"/>
+      <c r="D15" s="11">
+        <v>6</v>
+      </c>
       <c r="E15" s="11"/>
       <c r="F15" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>46</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -2901,7 +2947,7 @@
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="24" t="s">
         <v>45</v>
       </c>
       <c r="I16" s="1"/>
@@ -2969,19 +3015,19 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="20"/>
+      <c r="D19" s="11">
+        <v>6.5</v>
+      </c>
       <c r="E19" s="11"/>
       <c r="F19" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="G19" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>3.25</v>
+      </c>
+      <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -3059,7 +3105,7 @@
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="24" t="s">
         <v>45</v>
       </c>
       <c r="I22" s="1"/>
@@ -3180,20 +3226,18 @@
         <v>26</v>
       </c>
       <c r="D27" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27" s="11"/>
       <c r="F27" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G27" s="11">
         <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
@@ -3259,19 +3303,19 @@
       <c r="C30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="20"/>
+      <c r="D30" s="11">
+        <v>6.5</v>
+      </c>
       <c r="E30" s="11"/>
       <c r="F30" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="G30" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>3.25</v>
+      </c>
+      <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
   </sheetData>
@@ -3321,10 +3365,10 @@
         <v>27</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.3">
@@ -3351,7 +3395,7 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="24"/>
+      <c r="D4" s="23"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
@@ -3364,7 +3408,7 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="24"/>
+      <c r="D5" s="23"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
@@ -3377,7 +3421,7 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="24"/>
+      <c r="D6" s="23"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -3390,7 +3434,7 @@
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="24"/>
+      <c r="D7" s="23"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
@@ -3403,7 +3447,7 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="24"/>
+      <c r="D8" s="23"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
@@ -3416,10 +3460,10 @@
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="24"/>
+      <c r="D9" s="23"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="22">
+      <c r="A10" s="21">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -3429,10 +3473,10 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="24"/>
+      <c r="D10" s="23"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="22">
+      <c r="A11" s="21">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -3442,10 +3486,10 @@
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="23"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="23">
+      <c r="A12" s="22">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -3455,7 +3499,7 @@
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="24"/>
+      <c r="D12" s="23"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
@@ -3468,7 +3512,7 @@
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="24"/>
+      <c r="D13" s="23"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
@@ -3481,7 +3525,7 @@
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="24"/>
+      <c r="D14" s="23"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
@@ -3494,7 +3538,7 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="23"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
@@ -3507,7 +3551,7 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="24"/>
+      <c r="D16" s="23"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
@@ -3520,7 +3564,7 @@
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="24"/>
+      <c r="D17" s="23"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
@@ -3533,7 +3577,7 @@
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="24"/>
+      <c r="D18" s="23"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
@@ -3546,7 +3590,7 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="24"/>
+      <c r="D19" s="23"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
@@ -3559,7 +3603,7 @@
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="24"/>
+      <c r="D20" s="23"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
@@ -3572,7 +3616,7 @@
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="24"/>
+      <c r="D21" s="23"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
@@ -3585,7 +3629,7 @@
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="24"/>
+      <c r="D22" s="23"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
@@ -3598,7 +3642,7 @@
       <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="24"/>
+      <c r="D23" s="23"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
@@ -3611,7 +3655,7 @@
       <c r="C24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="24"/>
+      <c r="D24" s="23"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
@@ -3624,7 +3668,7 @@
       <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="24"/>
+      <c r="D25" s="23"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
@@ -3637,7 +3681,7 @@
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="24"/>
+      <c r="D26" s="23"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
@@ -3650,7 +3694,7 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="24"/>
+      <c r="D27" s="23"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
@@ -3663,7 +3707,7 @@
       <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="24"/>
+      <c r="D28" s="23"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
@@ -3676,7 +3720,7 @@
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="24"/>
+      <c r="D29" s="23"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
@@ -3689,7 +3733,7 @@
       <c r="C30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="24"/>
+      <c r="D30" s="23"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -3749,7 +3793,7 @@
         <v>27</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D2" s="29"/>
       <c r="E2" s="29"/>
@@ -3767,13 +3811,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>37</v>
@@ -3789,7 +3833,7 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="23">
         <f>_xlfn.XLOOKUP(B4,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>7.5</v>
       </c>
@@ -3801,7 +3845,7 @@
         <f>_xlfn.XLOOKUP(B4,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="20">
         <f>CEILING(SUM(D4:F4),0.5)</f>
         <v>11</v>
       </c>
@@ -3817,7 +3861,7 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="23">
         <f>_xlfn.XLOOKUP(B5,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>7.5</v>
       </c>
@@ -3829,7 +3873,7 @@
         <f>_xlfn.XLOOKUP(B5,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="20">
         <f t="shared" ref="G5:G30" si="0">CEILING(SUM(D5:F5),0.5)</f>
         <v>11</v>
       </c>
@@ -3845,7 +3889,7 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <f>_xlfn.XLOOKUP(B6,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>7.5</v>
       </c>
@@ -3857,7 +3901,7 @@
         <f>_xlfn.XLOOKUP(B6,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="20">
         <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
@@ -3873,9 +3917,9 @@
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="23">
         <f>_xlfn.XLOOKUP(B7,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="11">
         <f>_xlfn.XLOOKUP(B7,Assignment!$B$4:$B$30,Assignment!$G$4:$G$30)</f>
@@ -3885,9 +3929,9 @@
         <f>_xlfn.XLOOKUP(B7,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="21">
-        <f t="shared" si="0"/>
-        <v>11</v>
+      <c r="G7" s="20">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3901,9 +3945,9 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="23">
         <f>_xlfn.XLOOKUP(B8,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="E8" s="11">
         <f>_xlfn.XLOOKUP(B8,Assignment!$B$4:$B$30,Assignment!$G$4:$G$30)</f>
@@ -3913,9 +3957,9 @@
         <f>_xlfn.XLOOKUP(B8,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="21">
-        <f t="shared" si="0"/>
-        <v>11</v>
+      <c r="G8" s="20">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -3929,7 +3973,7 @@
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="23">
         <f>_xlfn.XLOOKUP(B9,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>7.5</v>
       </c>
@@ -3941,13 +3985,13 @@
         <f>_xlfn.XLOOKUP(B9,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="22">
+      <c r="A10" s="21">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -3957,7 +4001,7 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="23">
         <f>_xlfn.XLOOKUP(B10,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>0</v>
       </c>
@@ -3969,13 +4013,13 @@
         <f>_xlfn.XLOOKUP(B10,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="22">
+      <c r="A11" s="21">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -3985,7 +4029,7 @@
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="23">
         <f>_xlfn.XLOOKUP(B11,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>7.5</v>
       </c>
@@ -3997,13 +4041,13 @@
         <f>_xlfn.XLOOKUP(B11,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="23">
+      <c r="A12" s="22">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -4013,7 +4057,7 @@
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="23">
         <f>_xlfn.XLOOKUP(B12,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>7.5</v>
       </c>
@@ -4025,7 +4069,7 @@
         <f>_xlfn.XLOOKUP(B12,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -4041,7 +4085,7 @@
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="23">
         <f>_xlfn.XLOOKUP(B13,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>4.5</v>
       </c>
@@ -4053,7 +4097,7 @@
         <f>_xlfn.XLOOKUP(B13,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="20">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -4069,7 +4113,7 @@
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <f>_xlfn.XLOOKUP(B14,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>7.5</v>
       </c>
@@ -4081,7 +4125,7 @@
         <f>_xlfn.XLOOKUP(B14,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -4097,21 +4141,21 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="23">
         <f>_xlfn.XLOOKUP(B15,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>6</v>
       </c>
       <c r="E15" s="11">
         <f>_xlfn.XLOOKUP(B15,Assignment!$B$4:$B$30,Assignment!$G$4:$G$30)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" s="11">
         <f>_xlfn.XLOOKUP(B15,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="21">
-        <f t="shared" si="0"/>
-        <v>6</v>
+      <c r="G15" s="20">
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -4125,7 +4169,7 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <f>_xlfn.XLOOKUP(B16,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>6</v>
       </c>
@@ -4137,7 +4181,7 @@
         <f>_xlfn.XLOOKUP(B16,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="20">
         <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
@@ -4153,9 +4197,9 @@
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="23">
         <f>_xlfn.XLOOKUP(B17,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="E17" s="11">
         <f>_xlfn.XLOOKUP(B17,Assignment!$B$4:$B$30,Assignment!$G$4:$G$30)</f>
@@ -4165,9 +4209,9 @@
         <f>_xlfn.XLOOKUP(B17,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="21">
-        <f t="shared" si="0"/>
-        <v>9.5</v>
+      <c r="G17" s="20">
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -4181,7 +4225,7 @@
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="23">
         <f>_xlfn.XLOOKUP(B18,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>6</v>
       </c>
@@ -4193,7 +4237,7 @@
         <f>_xlfn.XLOOKUP(B18,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="20">
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
@@ -4209,21 +4253,21 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="23">
         <f>_xlfn.XLOOKUP(B19,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>3</v>
       </c>
       <c r="E19" s="11">
         <f>_xlfn.XLOOKUP(B19,Assignment!$B$4:$B$30,Assignment!$G$4:$G$30)</f>
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="F19" s="11">
         <f>_xlfn.XLOOKUP(B19,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="21">
-        <f t="shared" si="0"/>
-        <v>3</v>
+      <c r="G19" s="20">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -4237,7 +4281,7 @@
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="23">
         <f>_xlfn.XLOOKUP(B20,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>7.5</v>
       </c>
@@ -4249,7 +4293,7 @@
         <f>_xlfn.XLOOKUP(B20,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -4265,7 +4309,7 @@
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="23">
         <f>_xlfn.XLOOKUP(B21,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>7.5</v>
       </c>
@@ -4277,7 +4321,7 @@
         <f>_xlfn.XLOOKUP(B21,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -4293,7 +4337,7 @@
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="23">
         <f>_xlfn.XLOOKUP(B22,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>6</v>
       </c>
@@ -4305,7 +4349,7 @@
         <f>_xlfn.XLOOKUP(B22,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="20">
         <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
@@ -4321,7 +4365,7 @@
       <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="23">
         <f>_xlfn.XLOOKUP(B23,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>7.5</v>
       </c>
@@ -4333,7 +4377,7 @@
         <f>_xlfn.XLOOKUP(B23,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -4349,9 +4393,9 @@
       <c r="C24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="23">
         <f>_xlfn.XLOOKUP(B24,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="11">
         <f>_xlfn.XLOOKUP(B24,Assignment!$B$4:$B$30,Assignment!$G$4:$G$30)</f>
@@ -4361,9 +4405,9 @@
         <f>_xlfn.XLOOKUP(B24,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="21">
-        <f t="shared" si="0"/>
-        <v>11</v>
+      <c r="G24" s="20">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -4377,9 +4421,9 @@
       <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="23">
         <f>_xlfn.XLOOKUP(B25,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="E25" s="11">
         <f>_xlfn.XLOOKUP(B25,Assignment!$B$4:$B$30,Assignment!$G$4:$G$30)</f>
@@ -4389,9 +4433,9 @@
         <f>_xlfn.XLOOKUP(B25,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="21">
-        <f t="shared" si="0"/>
-        <v>9.5</v>
+      <c r="G25" s="20">
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -4405,7 +4449,7 @@
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="23">
         <f>_xlfn.XLOOKUP(B26,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>7.5</v>
       </c>
@@ -4417,7 +4461,7 @@
         <f>_xlfn.XLOOKUP(B26,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -4433,21 +4477,21 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="23">
         <f>_xlfn.XLOOKUP(B27,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>6</v>
       </c>
       <c r="E27" s="11">
         <f>_xlfn.XLOOKUP(B27,Assignment!$B$4:$B$30,Assignment!$G$4:$G$30)</f>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F27" s="11">
         <f>_xlfn.XLOOKUP(B27,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="21">
-        <f t="shared" si="0"/>
-        <v>8.5</v>
+      <c r="G27" s="20">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -4461,7 +4505,7 @@
       <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="23">
         <f>_xlfn.XLOOKUP(B28,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>4.5</v>
       </c>
@@ -4473,7 +4517,7 @@
         <f>_xlfn.XLOOKUP(B28,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="20">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -4489,7 +4533,7 @@
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="23">
         <f>_xlfn.XLOOKUP(B29,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>6</v>
       </c>
@@ -4501,7 +4545,7 @@
         <f>_xlfn.XLOOKUP(B29,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="21">
+      <c r="G29" s="20">
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
@@ -4517,21 +4561,21 @@
       <c r="C30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="23">
         <f>_xlfn.XLOOKUP(B30,'TFD 3-1 Attendance'!$B$4:$B$30,'TFD 3-1 Attendance'!$E$4:$E$30)</f>
         <v>6</v>
       </c>
       <c r="E30" s="11">
         <f>_xlfn.XLOOKUP(B30,Assignment!$B$4:$B$30,Assignment!$G$4:$G$30)</f>
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="F30" s="11">
         <f>_xlfn.XLOOKUP(B30,'Class Test'!$B$4:$B$30,'Class Test'!$D$4:$D$30)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="21">
-        <f t="shared" si="0"/>
-        <v>6</v>
+      <c r="G30" s="20">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
